--- a/data/trans_dic/P36B06_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36B06_R-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,31; 84,0</t>
+          <t>76,4; 83,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,49; 87,84</t>
+          <t>80,78; 88,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,59; 86,2</t>
+          <t>78,43; 86,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79,55; 88,1</t>
+          <t>80,16; 88,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,92; 94,03</t>
+          <t>87,33; 94,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,16; 88,94</t>
+          <t>81,73; 89,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,0; 84,59</t>
+          <t>79,17; 84,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>84,67; 89,45</t>
+          <t>84,46; 89,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81,27; 86,64</t>
+          <t>80,95; 86,6</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>74,34; 83,04</t>
+          <t>74,07; 82,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,41; 88,87</t>
+          <t>82,03; 89,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,14; 87,5</t>
+          <t>79,91; 87,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,54; 81,86</t>
+          <t>73,28; 82,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,1; 90,41</t>
+          <t>83,22; 90,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,25; 85,73</t>
+          <t>76,88; 85,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,12; 81,19</t>
+          <t>75,49; 81,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,49; 89,01</t>
+          <t>83,64; 88,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79,94; 85,81</t>
+          <t>80,0; 85,59</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,4; 79,84</t>
+          <t>72,78; 80,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,97; 85,13</t>
+          <t>78,59; 85,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,96; 82,32</t>
+          <t>74,46; 82,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74,74; 87,07</t>
+          <t>74,5; 87,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81,28; 89,98</t>
+          <t>81,63; 89,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,0; 90,1</t>
+          <t>78,73; 89,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,66; 80,79</t>
+          <t>74,32; 80,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80,34; 85,78</t>
+          <t>80,71; 85,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>76,84; 83,22</t>
+          <t>77,35; 83,7</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,0; 79,96</t>
+          <t>74,69; 79,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,0; 88,36</t>
+          <t>84,07; 88,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,08; 83,15</t>
+          <t>78,13; 83,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78,34; 84,16</t>
+          <t>78,37; 84,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,64; 88,08</t>
+          <t>83,09; 88,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,72; 81,59</t>
+          <t>75,55; 81,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,69; 80,61</t>
+          <t>76,81; 80,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84,47; 87,63</t>
+          <t>84,22; 87,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,92; 81,69</t>
+          <t>77,94; 81,56</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,86; 75,32</t>
+          <t>65,08; 75,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,89; 84,5</t>
+          <t>77,58; 84,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,46; 83,18</t>
+          <t>76,57; 83,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,63; 83,15</t>
+          <t>76,54; 83,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>85,09; 89,82</t>
+          <t>85,0; 89,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,6; 87,65</t>
+          <t>82,46; 87,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,23; 79,0</t>
+          <t>73,66; 79,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>82,81; 86,73</t>
+          <t>83,05; 87,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80,7; 84,86</t>
+          <t>80,6; 84,9</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,93; 73,15</t>
+          <t>62,53; 73,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67,37; 78,18</t>
+          <t>67,59; 78,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64,71; 75,75</t>
+          <t>64,33; 75,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80,97; 84,87</t>
+          <t>80,91; 85,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87,15; 90,77</t>
+          <t>87,18; 91,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82,85; 87,27</t>
+          <t>82,75; 87,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78,03; 82,01</t>
+          <t>78,13; 82,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83,96; 87,8</t>
+          <t>84,06; 87,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80,07; 84,09</t>
+          <t>80,03; 84,12</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>74,65; 77,72</t>
+          <t>74,63; 77,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,14; 84,71</t>
+          <t>82,14; 84,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,6; 81,45</t>
+          <t>78,51; 81,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,3; 83,04</t>
+          <t>80,39; 82,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,55; 88,83</t>
+          <t>86,63; 88,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,02; 84,63</t>
+          <t>82,07; 84,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,91; 79,96</t>
+          <t>77,92; 79,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>84,81; 86,54</t>
+          <t>84,75; 86,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>80,81; 82,67</t>
+          <t>80,77; 82,7</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>361530; 397985</t>
+          <t>361973; 396896</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>351925; 384050</t>
+          <t>353163; 384995</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>337240; 369896</t>
+          <t>336518; 371431</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>243974; 270189</t>
+          <t>245843; 271045</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>272369; 294659</t>
+          <t>273669; 294744</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>281667; 308672</t>
+          <t>283644; 309512</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>616539; 660208</t>
+          <t>617889; 660975</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>635480; 671428</t>
+          <t>633947; 673299</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>630801; 672482</t>
+          <t>628317; 672111</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>272118; 303956</t>
+          <t>271129; 303236</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>340098; 371256</t>
+          <t>342684; 372129</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>301580; 329274</t>
+          <t>300706; 329339</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>273456; 304408</t>
+          <t>272511; 305453</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>279182; 303743</t>
+          <t>279583; 304208</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>285467; 316804</t>
+          <t>284078; 315202</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>554316; 599105</t>
+          <t>557075; 601383</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>629290; 670856</t>
+          <t>630412; 669858</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>596227; 640040</t>
+          <t>596701; 638358</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>392714; 433054</t>
+          <t>394772; 435042</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>497031; 535835</t>
+          <t>494662; 536455</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>389122; 427310</t>
+          <t>386505; 427344</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>125400; 146089</t>
+          <t>124996; 146179</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>211421; 234068</t>
+          <t>212347; 233905</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>131234; 149678</t>
+          <t>130790; 149190</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>530224; 573781</t>
+          <t>527801; 573009</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>714658; 763029</t>
+          <t>717948; 763561</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>526505; 570253</t>
+          <t>530002; 573518</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>928001; 989408</t>
+          <t>924151; 987643</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>971948; 1022320</t>
+          <t>972687; 1021093</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>895970; 954165</t>
+          <t>896621; 953096</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>559588; 601116</t>
+          <t>559791; 602346</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>631939; 673583</t>
+          <t>635447; 674677</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>624588; 672983</t>
+          <t>623170; 672926</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1496718; 1573152</t>
+          <t>1499078; 1572838</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1623261; 1684118</t>
+          <t>1618579; 1682385</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1536931; 1611309</t>
+          <t>1537363; 1608757</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>230865; 264047</t>
+          <t>228144; 263207</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>396120; 429749</t>
+          <t>394527; 430675</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474568; 516327</t>
+          <t>475249; 517672</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>435008; 472025</t>
+          <t>434521; 472027</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>647947; 684006</t>
+          <t>647284; 685213</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>608874; 646111</t>
+          <t>607839; 647272</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>672397; 725452</t>
+          <t>676340; 726306</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1051752; 1101587</t>
+          <t>1054849; 1106570</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1095825; 1152236</t>
+          <t>1094502; 1152806</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>187005; 217377</t>
+          <t>185821; 217930</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>179795; 208641</t>
+          <t>180392; 208874</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>185160; 216777</t>
+          <t>184095; 215336</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1010301; 1059043</t>
+          <t>1009531; 1062140</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>964800; 1004937</t>
+          <t>965182; 1008647</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>895653; 943458</t>
+          <t>894510; 943959</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1205494; 1267002</t>
+          <t>1207097; 1269147</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1153553; 1206366</t>
+          <t>1154911; 1205463</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1094670; 1149620</t>
+          <t>1094188; 1150013</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2439055; 2539462</t>
+          <t>2438510; 2540339</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2806520; 2894389</t>
+          <t>2806499; 2896366</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2655876; 2752146</t>
+          <t>2652640; 2748161</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2711090; 2803628</t>
+          <t>2714021; 2798435</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3066309; 3147187</t>
+          <t>3069249; 3146952</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2891807; 2983797</t>
+          <t>2893553; 2982734</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5175696; 5312330</t>
+          <t>5176475; 5309890</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5902771; 6022539</t>
+          <t>5898148; 6018559</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5579892; 5708220</t>
+          <t>5576578; 5710344</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36B06_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36B06_R-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,4; 83,77</t>
+          <t>76,47; 83,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,78; 88,06</t>
+          <t>80,47; 87,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,43; 86,56</t>
+          <t>78,8; 86,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80,16; 88,38</t>
+          <t>80,29; 87,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,33; 94,06</t>
+          <t>87,26; 94,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,73; 89,18</t>
+          <t>81,51; 89,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,17; 84,69</t>
+          <t>79,04; 84,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>84,46; 89,7</t>
+          <t>84,33; 89,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>80,95; 86,6</t>
+          <t>80,74; 86,76</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>74,07; 82,84</t>
+          <t>74,32; 82,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,03; 89,08</t>
+          <t>81,68; 89,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,91; 87,51</t>
+          <t>79,87; 87,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,28; 82,14</t>
+          <t>73,21; 82,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,22; 90,55</t>
+          <t>83,33; 90,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,88; 85,3</t>
+          <t>76,92; 85,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,49; 81,5</t>
+          <t>75,32; 81,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,64; 88,87</t>
+          <t>83,43; 88,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,0; 85,59</t>
+          <t>80,2; 85,63</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,78; 80,21</t>
+          <t>72,84; 80,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,59; 85,23</t>
+          <t>79,14; 85,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,46; 82,32</t>
+          <t>75,05; 82,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74,5; 87,12</t>
+          <t>74,69; 87,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81,63; 89,92</t>
+          <t>80,72; 89,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,73; 89,81</t>
+          <t>77,91; 89,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,32; 80,69</t>
+          <t>74,39; 80,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80,71; 85,84</t>
+          <t>80,85; 85,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77,35; 83,7</t>
+          <t>77,11; 83,3</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,69; 79,82</t>
+          <t>74,91; 79,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,07; 88,25</t>
+          <t>83,91; 88,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,13; 83,06</t>
+          <t>77,9; 82,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78,37; 84,33</t>
+          <t>78,28; 84,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,09; 88,22</t>
+          <t>82,98; 88,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,55; 81,58</t>
+          <t>75,62; 81,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,81; 80,59</t>
+          <t>76,83; 80,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84,22; 87,54</t>
+          <t>84,19; 87,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,94; 81,56</t>
+          <t>77,87; 81,54</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,08; 75,08</t>
+          <t>65,36; 75,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,58; 84,68</t>
+          <t>77,5; 84,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,57; 83,4</t>
+          <t>76,61; 83,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,54; 83,15</t>
+          <t>76,57; 83,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>85,0; 89,98</t>
+          <t>84,82; 90,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,46; 87,81</t>
+          <t>82,51; 87,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,66; 79,1</t>
+          <t>73,28; 79,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,05; 87,13</t>
+          <t>82,85; 86,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80,6; 84,9</t>
+          <t>80,8; 85,04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,53; 73,34</t>
+          <t>62,83; 73,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67,59; 78,26</t>
+          <t>67,49; 78,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64,33; 75,25</t>
+          <t>64,26; 75,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80,91; 85,12</t>
+          <t>80,73; 84,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87,18; 91,11</t>
+          <t>86,83; 90,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82,75; 87,32</t>
+          <t>82,91; 87,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78,13; 82,15</t>
+          <t>78,22; 82,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84,06; 87,74</t>
+          <t>84,0; 87,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80,03; 84,12</t>
+          <t>80,0; 84,06</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>74,63; 77,75</t>
+          <t>74,57; 77,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,14; 84,77</t>
+          <t>82,09; 84,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,51; 81,33</t>
+          <t>78,72; 81,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,39; 82,89</t>
+          <t>80,28; 82,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,63; 88,83</t>
+          <t>86,55; 88,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,07; 84,6</t>
+          <t>81,8; 84,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,92; 79,93</t>
+          <t>77,92; 79,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>84,75; 86,48</t>
+          <t>84,69; 86,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>80,77; 82,7</t>
+          <t>80,71; 82,65</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>361973; 396896</t>
+          <t>362281; 395894</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>353163; 384995</t>
+          <t>351824; 383904</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>336518; 371431</t>
+          <t>338110; 370787</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>245843; 271045</t>
+          <t>246242; 269684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>273669; 294744</t>
+          <t>273442; 295140</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>283644; 309512</t>
+          <t>282875; 309158</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>617889; 660975</t>
+          <t>616896; 661969</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>633947; 673299</t>
+          <t>632987; 672370</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>628317; 672111</t>
+          <t>626664; 673363</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>271129; 303236</t>
+          <t>272054; 303409</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>342684; 372129</t>
+          <t>341217; 372121</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>300706; 329339</t>
+          <t>300580; 329751</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>272511; 305453</t>
+          <t>272258; 305029</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>279583; 304208</t>
+          <t>279972; 304983</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>284078; 315202</t>
+          <t>284250; 315489</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>557075; 601383</t>
+          <t>555797; 599792</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>630412; 669858</t>
+          <t>628812; 667601</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>596701; 638358</t>
+          <t>598153; 638698</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>394772; 435042</t>
+          <t>395067; 435002</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>494662; 536455</t>
+          <t>498141; 536563</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>386505; 427344</t>
+          <t>389565; 427703</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124996; 146179</t>
+          <t>125323; 146625</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>212347; 233905</t>
+          <t>209973; 233916</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>130790; 149190</t>
+          <t>129432; 148991</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>527801; 573009</t>
+          <t>528325; 572686</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>717948; 763561</t>
+          <t>719166; 764076</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>530002; 573518</t>
+          <t>528376; 570769</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>924151; 987643</t>
+          <t>926886; 986797</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>972687; 1021093</t>
+          <t>970893; 1019670</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>896621; 953096</t>
+          <t>893906; 949839</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>559791; 602346</t>
+          <t>559128; 601901</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>635447; 674677</t>
+          <t>634540; 674355</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>623170; 672926</t>
+          <t>623753; 670545</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1499078; 1572838</t>
+          <t>1499562; 1570343</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1618579; 1682385</t>
+          <t>1617901; 1680224</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1537363; 1608757</t>
+          <t>1535812; 1608234</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>228144; 263207</t>
+          <t>229113; 262964</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>394527; 430675</t>
+          <t>394152; 429197</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475249; 517672</t>
+          <t>475533; 516401</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>434521; 472027</t>
+          <t>434676; 472441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>647284; 685213</t>
+          <t>645953; 685517</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>607839; 647272</t>
+          <t>608256; 648207</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>676340; 726306</t>
+          <t>672910; 726506</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1054849; 1106570</t>
+          <t>1052325; 1103858</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1094502; 1152806</t>
+          <t>1097170; 1154723</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>185821; 217930</t>
+          <t>186719; 218562</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>180392; 208874</t>
+          <t>180110; 208461</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>184095; 215336</t>
+          <t>183883; 214972</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1009531; 1062140</t>
+          <t>1007345; 1058923</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>965182; 1008647</t>
+          <t>961298; 1005098</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>894510; 943959</t>
+          <t>896246; 943884</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1207097; 1269147</t>
+          <t>1208521; 1267449</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1154911; 1205463</t>
+          <t>1154122; 1206977</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1094188; 1150013</t>
+          <t>1093792; 1149321</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2438510; 2540339</t>
+          <t>2436486; 2537952</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2806499; 2896366</t>
+          <t>2804895; 2895501</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2652640; 2748161</t>
+          <t>2659933; 2749604</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2714021; 2798435</t>
+          <t>2710333; 2798140</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3069249; 3146952</t>
+          <t>3066359; 3148196</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2893553; 2982734</t>
+          <t>2883915; 2983030</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5176475; 5309890</t>
+          <t>5176711; 5309109</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5898148; 6018559</t>
+          <t>5894273; 6015919</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5576578; 5710344</t>
+          <t>5572924; 5706778</t>
         </is>
       </c>
     </row>
